--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/133.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/133.xlsx
@@ -426,13 +426,13 @@
         <v>-20.54341643231632</v>
       </c>
       <c r="E2">
-        <v>-21.04315510467262</v>
+        <v>-23.29297344726738</v>
       </c>
       <c r="F2">
-        <v>-5.264229431831212</v>
+        <v>-5.769974238997199</v>
       </c>
       <c r="G2">
-        <v>-14.58750459600164</v>
+        <v>-14.74054780573661</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-20.20510563768072</v>
       </c>
       <c r="E3">
-        <v>-22.1093752528306</v>
+        <v>-23.55614571422315</v>
       </c>
       <c r="F3">
-        <v>-5.399235922772073</v>
+        <v>-6.265952594484181</v>
       </c>
       <c r="G3">
-        <v>-14.49518175727522</v>
+        <v>-14.4015992559711</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-19.69275759635666</v>
       </c>
       <c r="E4">
-        <v>-23.35475994662804</v>
+        <v>-23.93462198636221</v>
       </c>
       <c r="F4">
-        <v>-5.378303078503329</v>
+        <v>-6.085788482947108</v>
       </c>
       <c r="G4">
-        <v>-14.14563118542019</v>
+        <v>-13.56313738723988</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-19.03730683643798</v>
       </c>
       <c r="E5">
-        <v>-24.0176832566109</v>
+        <v>-24.24455074744717</v>
       </c>
       <c r="F5">
-        <v>-5.601036990870268</v>
+        <v>-6.067879179698583</v>
       </c>
       <c r="G5">
-        <v>-14.05796628426752</v>
+        <v>-13.89630241394829</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-18.22748082983391</v>
       </c>
       <c r="E6">
-        <v>-24.12977657372276</v>
+        <v>-25.23385023611085</v>
       </c>
       <c r="F6">
-        <v>-5.752944661930448</v>
+        <v>-5.820567606490583</v>
       </c>
       <c r="G6">
-        <v>-13.61477527656144</v>
+        <v>-13.1851558502936</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.28003520794071</v>
       </c>
       <c r="E7">
-        <v>-24.79998166990996</v>
+        <v>-25.9838470443132</v>
       </c>
       <c r="F7">
-        <v>-5.845281947953105</v>
+        <v>-6.09888248648316</v>
       </c>
       <c r="G7">
-        <v>-13.46388723197254</v>
+        <v>-13.30752685560722</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-16.20850917931715</v>
       </c>
       <c r="E8">
-        <v>-24.04751231489942</v>
+        <v>-25.84830076031561</v>
       </c>
       <c r="F8">
-        <v>-5.796190410560999</v>
+        <v>-6.199212689575431</v>
       </c>
       <c r="G8">
-        <v>-13.73621767385129</v>
+        <v>-13.23236091913807</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-15.02710989585501</v>
       </c>
       <c r="E9">
-        <v>-24.8745701652903</v>
+        <v>-26.0351546548201</v>
       </c>
       <c r="F9">
-        <v>-6.102963024309351</v>
+        <v>-6.521598372131748</v>
       </c>
       <c r="G9">
-        <v>-13.41026301532742</v>
+        <v>-12.69531429012087</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.74686122721706</v>
       </c>
       <c r="E10">
-        <v>-24.28904300457253</v>
+        <v>-26.92815161523667</v>
       </c>
       <c r="F10">
-        <v>-5.904927714424281</v>
+        <v>-6.727757481136072</v>
       </c>
       <c r="G10">
-        <v>-12.74840219838863</v>
+        <v>-11.990664672087</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-12.39810911318673</v>
       </c>
       <c r="E11">
-        <v>-27.18681352208079</v>
+        <v>-27.79757786844331</v>
       </c>
       <c r="F11">
-        <v>-6.444280629672949</v>
+        <v>-6.403930439298883</v>
       </c>
       <c r="G11">
-        <v>-11.3591847315621</v>
+        <v>-12.5622071856234</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-11.01052427090341</v>
       </c>
       <c r="E12">
-        <v>-27.74452679544345</v>
+        <v>-27.81828658008039</v>
       </c>
       <c r="F12">
-        <v>-6.030303605940195</v>
+        <v>-6.640814523640445</v>
       </c>
       <c r="G12">
-        <v>-11.47017077076617</v>
+        <v>-11.53328301092684</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.61306472158488</v>
       </c>
       <c r="E13">
-        <v>-28.03563521855253</v>
+        <v>-28.51629650667468</v>
       </c>
       <c r="F13">
-        <v>-5.675712655497838</v>
+        <v>-6.540631769945872</v>
       </c>
       <c r="G13">
-        <v>-10.10834475773157</v>
+        <v>-10.89409943093205</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.26012685879981</v>
       </c>
       <c r="E14">
-        <v>-27.27259187673408</v>
+        <v>-28.93407993320032</v>
       </c>
       <c r="F14">
-        <v>-6.52485385602475</v>
+        <v>-6.310938743028014</v>
       </c>
       <c r="G14">
-        <v>-10.46774751311147</v>
+        <v>-10.38825138307695</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.004345589242152</v>
       </c>
       <c r="E15">
-        <v>-30.33677249283921</v>
+        <v>-29.29002251867722</v>
       </c>
       <c r="F15">
-        <v>-6.269097905512611</v>
+        <v>-6.338294748138065</v>
       </c>
       <c r="G15">
-        <v>-10.33450798679242</v>
+        <v>-10.41037906946144</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.892029303240159</v>
       </c>
       <c r="E16">
-        <v>-30.77043048499874</v>
+        <v>-30.66514572855741</v>
       </c>
       <c r="F16">
-        <v>-6.169338447560869</v>
+        <v>-6.324660649055388</v>
       </c>
       <c r="G16">
-        <v>-9.148793064810437</v>
+        <v>-9.147746932420027</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.975637844785975</v>
       </c>
       <c r="E17">
-        <v>-30.91623829109772</v>
+        <v>-30.76493291755343</v>
       </c>
       <c r="F17">
-        <v>-6.186290986459161</v>
+        <v>-6.252439022858612</v>
       </c>
       <c r="G17">
-        <v>-8.418172217020983</v>
+        <v>-9.79774606469161</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.293525832899032</v>
       </c>
       <c r="E18">
-        <v>-30.33130209623795</v>
+        <v>-31.39789810773855</v>
       </c>
       <c r="F18">
-        <v>-6.178216061016672</v>
+        <v>-6.183424006878072</v>
       </c>
       <c r="G18">
-        <v>-9.043507785024996</v>
+        <v>-9.250022926310272</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-3.855952079499363</v>
       </c>
       <c r="E19">
-        <v>-30.93949426936411</v>
+        <v>-31.18161139642121</v>
       </c>
       <c r="F19">
-        <v>-5.893491274061232</v>
+        <v>-6.32925353212021</v>
       </c>
       <c r="G19">
-        <v>-8.577935834200671</v>
+        <v>-9.406283986309411</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.654232541169226</v>
       </c>
       <c r="E20">
-        <v>-30.54592232912047</v>
+        <v>-32.32659529299459</v>
       </c>
       <c r="F20">
-        <v>-6.053693387925642</v>
+        <v>-6.107766726878185</v>
       </c>
       <c r="G20">
-        <v>-7.721087195544345</v>
+        <v>-9.140864308243883</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.660486357775854</v>
       </c>
       <c r="E21">
-        <v>-32.54643459217095</v>
+        <v>-32.76604067493592</v>
       </c>
       <c r="F21">
-        <v>-5.72248559252951</v>
+        <v>-5.800542652895307</v>
       </c>
       <c r="G21">
-        <v>-8.630295422449784</v>
+        <v>-9.208945677258995</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.824341201119153</v>
       </c>
       <c r="E22">
-        <v>-31.68947749214443</v>
+        <v>-33.74965692871998</v>
       </c>
       <c r="F22">
-        <v>-5.519875209478778</v>
+        <v>-5.688472826970562</v>
       </c>
       <c r="G22">
-        <v>-8.079020068704807</v>
+        <v>-9.625879093020348</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.08680529802988</v>
       </c>
       <c r="E23">
-        <v>-33.39240335001786</v>
+        <v>-32.04300866521225</v>
       </c>
       <c r="F23">
-        <v>-5.560533966710387</v>
+        <v>-5.406902463084982</v>
       </c>
       <c r="G23">
-        <v>-7.413477925126345</v>
+        <v>-9.430831681483108</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.394282242388937</v>
       </c>
       <c r="E24">
-        <v>-34.21901061724497</v>
+        <v>-33.29553023404578</v>
       </c>
       <c r="F24">
-        <v>-5.754423297744444</v>
+        <v>-5.283115380247638</v>
       </c>
       <c r="G24">
-        <v>-8.269359884485203</v>
+        <v>-9.110698617290044</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.69506900516718</v>
       </c>
       <c r="E25">
-        <v>-33.34545892421735</v>
+        <v>-33.52632164760969</v>
       </c>
       <c r="F25">
-        <v>-5.278607404841603</v>
+        <v>-5.417084755200194</v>
       </c>
       <c r="G25">
-        <v>-9.621595247092531</v>
+        <v>-9.542506314159342</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-4.948226119221612</v>
       </c>
       <c r="E26">
-        <v>-33.95423074201648</v>
+        <v>-33.82431787968444</v>
       </c>
       <c r="F26">
-        <v>-5.089745435575136</v>
+        <v>-5.331038919601798</v>
       </c>
       <c r="G26">
-        <v>-7.589363899082284</v>
+        <v>-10.20682686643381</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.134308774997671</v>
       </c>
       <c r="E27">
-        <v>-33.91420356026268</v>
+        <v>-34.02415038069491</v>
       </c>
       <c r="F27">
-        <v>-5.412897357979042</v>
+        <v>-5.070331817123126</v>
       </c>
       <c r="G27">
-        <v>-9.24254109339152</v>
+        <v>-10.71388326341074</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.24409909254614</v>
       </c>
       <c r="E28">
-        <v>-33.43719448642773</v>
+        <v>-33.29485775565563</v>
       </c>
       <c r="F28">
-        <v>-5.375449352800684</v>
+        <v>-5.312744425510971</v>
       </c>
       <c r="G28">
-        <v>-9.520832172513733</v>
+        <v>-10.07901332425363</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.278365470070227</v>
       </c>
       <c r="E29">
-        <v>-33.58920856615421</v>
+        <v>-33.28372450230778</v>
       </c>
       <c r="F29">
-        <v>-4.979142648320748</v>
+        <v>-5.129691796840336</v>
       </c>
       <c r="G29">
-        <v>-8.969278732943458</v>
+        <v>-10.38785411761224</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.25007323247664</v>
       </c>
       <c r="E30">
-        <v>-33.59389780098915</v>
+        <v>-33.81855313227268</v>
       </c>
       <c r="F30">
-        <v>-4.791143837887997</v>
+        <v>-5.085538985903719</v>
       </c>
       <c r="G30">
-        <v>-10.5577314514144</v>
+        <v>-10.74767731227563</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.174254999821778</v>
       </c>
       <c r="E31">
-        <v>-32.87716263437314</v>
+        <v>-33.19130287628523</v>
       </c>
       <c r="F31">
-        <v>-4.441861894130184</v>
+        <v>-5.105856353192183</v>
       </c>
       <c r="G31">
-        <v>-9.195912059470885</v>
+        <v>-11.01715240862676</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.063278208177179</v>
       </c>
       <c r="E32">
-        <v>-32.38437635709546</v>
+        <v>-33.28753294894823</v>
       </c>
       <c r="F32">
-        <v>-4.929756212133245</v>
+        <v>-4.626117312269683</v>
       </c>
       <c r="G32">
-        <v>-9.779163972579681</v>
+        <v>-10.80369174280009</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.928758851656912</v>
       </c>
       <c r="E33">
-        <v>-31.84971980914285</v>
+        <v>-32.85646750815809</v>
       </c>
       <c r="F33">
-        <v>-5.176470532443827</v>
+        <v>-4.996061224155525</v>
       </c>
       <c r="G33">
-        <v>-9.789317415748627</v>
+        <v>-11.18031926662082</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.777834242973765</v>
       </c>
       <c r="E34">
-        <v>-33.46125879730449</v>
+        <v>-32.51253443574953</v>
       </c>
       <c r="F34">
-        <v>-5.09054563848624</v>
+        <v>-5.178461099312754</v>
       </c>
       <c r="G34">
-        <v>-9.380829201657955</v>
+        <v>-11.0974430695907</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.612143623249005</v>
       </c>
       <c r="E35">
-        <v>-30.71451741642604</v>
+        <v>-32.29334270835626</v>
       </c>
       <c r="F35">
-        <v>-4.886158407356503</v>
+        <v>-4.734177011597476</v>
       </c>
       <c r="G35">
-        <v>-10.28346930621348</v>
+        <v>-10.27999323339725</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.430701791532696</v>
       </c>
       <c r="E36">
-        <v>-31.74319425082342</v>
+        <v>-32.02085989884073</v>
       </c>
       <c r="F36">
-        <v>-4.621263079289277</v>
+        <v>-4.920510803550599</v>
       </c>
       <c r="G36">
-        <v>-8.714151540959524</v>
+        <v>-10.51738252238176</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.234965251912066</v>
       </c>
       <c r="E37">
-        <v>-30.77430459451231</v>
+        <v>-31.14891581408583</v>
       </c>
       <c r="F37">
-        <v>-4.684672118871371</v>
+        <v>-4.9938345725768</v>
       </c>
       <c r="G37">
-        <v>-10.58539436994055</v>
+        <v>-10.63111962492897</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.025778686643217</v>
       </c>
       <c r="E38">
-        <v>-31.24729238342846</v>
+        <v>-31.21329486481587</v>
       </c>
       <c r="F38">
-        <v>-4.584240026588557</v>
+        <v>-4.714542219048919</v>
       </c>
       <c r="G38">
-        <v>-9.719382141231524</v>
+        <v>-10.89094117048758</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.804657999065804</v>
       </c>
       <c r="E39">
-        <v>-29.85852940983716</v>
+        <v>-30.60906284220942</v>
       </c>
       <c r="F39">
-        <v>-4.595823087981902</v>
+        <v>-4.756527192492409</v>
       </c>
       <c r="G39">
-        <v>-9.41291831957011</v>
+        <v>-10.26095759654643</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.580760396330756</v>
       </c>
       <c r="E40">
-        <v>-28.65483158351733</v>
+        <v>-29.93141972746462</v>
       </c>
       <c r="F40">
-        <v>-4.634190580977367</v>
+        <v>-4.904446274508108</v>
       </c>
       <c r="G40">
-        <v>-10.59079055916956</v>
+        <v>-10.80080163654431</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.363201453020126</v>
       </c>
       <c r="E41">
-        <v>-28.80889479773228</v>
+        <v>-30.34819556852356</v>
       </c>
       <c r="F41">
-        <v>-4.351589728042704</v>
+        <v>-4.796212618025728</v>
       </c>
       <c r="G41">
-        <v>-8.980362439408937</v>
+        <v>-9.922795301346502</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.159099632636936</v>
       </c>
       <c r="E42">
-        <v>-30.84754134040136</v>
+        <v>-29.61081735314358</v>
       </c>
       <c r="F42">
-        <v>-4.095547990776599</v>
+        <v>-4.581579310490764</v>
       </c>
       <c r="G42">
-        <v>-8.853565234709311</v>
+        <v>-9.578362832895188</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.980614253901136</v>
       </c>
       <c r="E43">
-        <v>-29.4102716174769</v>
+        <v>-29.35474346919484</v>
       </c>
       <c r="F43">
-        <v>-4.961878643279004</v>
+        <v>-4.430961407476745</v>
       </c>
       <c r="G43">
-        <v>-9.870587998192194</v>
+        <v>-10.50970205673065</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-2.840391108498834</v>
       </c>
       <c r="E44">
-        <v>-29.67206949257134</v>
+        <v>-29.25772091358051</v>
       </c>
       <c r="F44">
-        <v>-4.837399873660322</v>
+        <v>-4.638188282063277</v>
       </c>
       <c r="G44">
-        <v>-9.220297537913156</v>
+        <v>-9.918633945603638</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.748299418407294</v>
       </c>
       <c r="E45">
-        <v>-27.39875516258778</v>
+        <v>-28.3628084086587</v>
       </c>
       <c r="F45">
-        <v>-4.471772584310468</v>
+        <v>-4.711175733923942</v>
       </c>
       <c r="G45">
-        <v>-9.134325980803823</v>
+        <v>-10.44401421214044</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.71536444858561</v>
       </c>
       <c r="E46">
-        <v>-25.79248731817107</v>
+        <v>-27.73503511392337</v>
       </c>
       <c r="F46">
-        <v>-4.482143744193517</v>
+        <v>-4.666865533180793</v>
       </c>
       <c r="G46">
-        <v>-8.747055053074339</v>
+        <v>-9.521689603808404</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.749581209921659</v>
       </c>
       <c r="E47">
-        <v>-25.65692292027746</v>
+        <v>-28.40425753125091</v>
       </c>
       <c r="F47">
-        <v>-4.523036929400118</v>
+        <v>-4.736241303165252</v>
       </c>
       <c r="G47">
-        <v>-9.73234292701777</v>
+        <v>-10.11677009612902</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-2.851265262637998</v>
       </c>
       <c r="E48">
-        <v>-26.81166114986336</v>
+        <v>-28.09019880187095</v>
       </c>
       <c r="F48">
-        <v>-4.271331695487668</v>
+        <v>-4.40091155157279</v>
       </c>
       <c r="G48">
-        <v>-10.04336536988676</v>
+        <v>-10.80461869555109</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.016572613694865</v>
       </c>
       <c r="E49">
-        <v>-26.23176288233712</v>
+        <v>-28.42083174611898</v>
       </c>
       <c r="F49">
-        <v>-4.602677828240068</v>
+        <v>-4.729337689230321</v>
       </c>
       <c r="G49">
-        <v>-9.462185858285544</v>
+        <v>-9.942274551299572</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.239749434538582</v>
       </c>
       <c r="E50">
-        <v>-24.7076687272636</v>
+        <v>-26.60365928174304</v>
       </c>
       <c r="F50">
-        <v>-4.613053129960131</v>
+        <v>-4.691504493209662</v>
       </c>
       <c r="G50">
-        <v>-10.18732113211643</v>
+        <v>-10.11916362055391</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.508623426477905</v>
       </c>
       <c r="E51">
-        <v>-24.65429160413519</v>
+        <v>-26.87140530744655</v>
       </c>
       <c r="F51">
-        <v>-4.269638512516346</v>
+        <v>-4.543881966724165</v>
       </c>
       <c r="G51">
-        <v>-9.447834643372804</v>
+        <v>-10.33663997811971</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.808063651016889</v>
       </c>
       <c r="E52">
-        <v>-24.21704932479859</v>
+        <v>-25.38122489421648</v>
       </c>
       <c r="F52">
-        <v>-3.693910742059648</v>
+        <v>-4.63667402645096</v>
       </c>
       <c r="G52">
-        <v>-8.96827232709952</v>
+        <v>-10.75134870727868</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.125558559080702</v>
       </c>
       <c r="E53">
-        <v>-24.45136162690347</v>
+        <v>-25.46511487520857</v>
       </c>
       <c r="F53">
-        <v>-4.704530570618684</v>
+        <v>-4.876285096282536</v>
       </c>
       <c r="G53">
-        <v>-10.97576065774925</v>
+        <v>-10.53404449808092</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.446263678072204</v>
       </c>
       <c r="E54">
-        <v>-23.33583998222399</v>
+        <v>-25.06315846533973</v>
       </c>
       <c r="F54">
-        <v>-4.312851954818188</v>
+        <v>-4.608965965194719</v>
       </c>
       <c r="G54">
-        <v>-9.95418920469541</v>
+        <v>-10.73856669095155</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.755165844584226</v>
       </c>
       <c r="E55">
-        <v>-22.66028675823373</v>
+        <v>-25.11322980244254</v>
       </c>
       <c r="F55">
-        <v>-4.644618069843807</v>
+        <v>-4.87175889679364</v>
       </c>
       <c r="G55">
-        <v>-10.06660871011798</v>
+        <v>-10.88066192658815</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.044106782300275</v>
       </c>
       <c r="E56">
-        <v>-22.80748480585306</v>
+        <v>-24.68206926369824</v>
       </c>
       <c r="F56">
-        <v>-3.881530160221916</v>
+        <v>-4.824491424422497</v>
       </c>
       <c r="G56">
-        <v>-10.21317980332367</v>
+        <v>-10.69403985344835</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.305132211156927</v>
       </c>
       <c r="E57">
-        <v>-23.60109987569729</v>
+        <v>-25.32596845437488</v>
       </c>
       <c r="F57">
-        <v>-4.601069967111235</v>
+        <v>-4.832127315141503</v>
       </c>
       <c r="G57">
-        <v>-10.58437472191446</v>
+        <v>-10.63656878288661</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.530122372994431</v>
       </c>
       <c r="E58">
-        <v>-22.15823295889935</v>
+        <v>-24.91898543835753</v>
       </c>
       <c r="F58">
-        <v>-4.360185696581555</v>
+        <v>-4.606312704403552</v>
       </c>
       <c r="G58">
-        <v>-10.75381837425097</v>
+        <v>-10.38483490008042</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.716895407713918</v>
       </c>
       <c r="E59">
-        <v>-21.72616672535352</v>
+        <v>-23.90854250455204</v>
       </c>
       <c r="F59">
-        <v>-4.108751338809821</v>
+        <v>-4.591581846879569</v>
       </c>
       <c r="G59">
-        <v>-10.73635193598578</v>
+        <v>-11.28675661625393</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.864225288562579</v>
       </c>
       <c r="E60">
-        <v>-22.11225083382547</v>
+        <v>-24.14341633743387</v>
       </c>
       <c r="F60">
-        <v>-4.593212073928278</v>
+        <v>-4.577996621473657</v>
       </c>
       <c r="G60">
-        <v>-10.57818731230156</v>
+        <v>-11.35975083484932</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.970621950226326</v>
       </c>
       <c r="E61">
-        <v>-22.71164418195472</v>
+        <v>-23.32835894316332</v>
       </c>
       <c r="F61">
-        <v>-4.425495839353073</v>
+        <v>-4.566952827259533</v>
       </c>
       <c r="G61">
-        <v>-10.63166586494294</v>
+        <v>-11.38160043540851</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.036981689461471</v>
       </c>
       <c r="E62">
-        <v>-21.47919280992319</v>
+        <v>-22.95052118585933</v>
       </c>
       <c r="F62">
-        <v>-4.123436636126651</v>
+        <v>-4.339309181296201</v>
       </c>
       <c r="G62">
-        <v>-11.12234168259156</v>
+        <v>-12.09095764919922</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.066865622237762</v>
       </c>
       <c r="E63">
-        <v>-21.17016068669175</v>
+        <v>-23.4541599510964</v>
       </c>
       <c r="F63">
-        <v>-4.469841659894542</v>
+        <v>-4.669857596239705</v>
       </c>
       <c r="G63">
-        <v>-11.27249478607075</v>
+        <v>-11.78767195125551</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.061491995589307</v>
       </c>
       <c r="E64">
-        <v>-21.67533913309142</v>
+        <v>-23.14323492572975</v>
       </c>
       <c r="F64">
-        <v>-4.341351935311505</v>
+        <v>-4.883213561239551</v>
       </c>
       <c r="G64">
-        <v>-10.70161107109667</v>
+        <v>-11.41958894547165</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.020929985958011</v>
       </c>
       <c r="E65">
-        <v>-20.22436624781976</v>
+        <v>-23.22174960807474</v>
       </c>
       <c r="F65">
-        <v>-4.242693377638084</v>
+        <v>-4.844416145562033</v>
       </c>
       <c r="G65">
-        <v>-11.5764326614857</v>
+        <v>-11.86546977142838</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.949331853982825</v>
       </c>
       <c r="E66">
-        <v>-21.89631507924371</v>
+        <v>-23.36491278535323</v>
       </c>
       <c r="F66">
-        <v>-4.516385967523041</v>
+        <v>-4.602935450502339</v>
       </c>
       <c r="G66">
-        <v>-10.8233762465766</v>
+        <v>-11.61171314529771</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.848222756564049</v>
       </c>
       <c r="E67">
-        <v>-20.84062363315358</v>
+        <v>-22.41641031902465</v>
       </c>
       <c r="F67">
-        <v>-4.682045365837094</v>
+        <v>-4.512461162768576</v>
       </c>
       <c r="G67">
-        <v>-11.25481647289104</v>
+        <v>-11.32873433369189</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.716421667072919</v>
       </c>
       <c r="E68">
-        <v>-20.78320258273632</v>
+        <v>-22.5179839910167</v>
       </c>
       <c r="F68">
-        <v>-4.679975275697498</v>
+        <v>-4.789747210446878</v>
       </c>
       <c r="G68">
-        <v>-12.12399358313561</v>
+        <v>-11.54037419947195</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.557783890969079</v>
       </c>
       <c r="E69">
-        <v>-19.39469546792645</v>
+        <v>-22.17559059977075</v>
       </c>
       <c r="F69">
-        <v>-4.126585260624691</v>
+        <v>-4.520791225371129</v>
       </c>
       <c r="G69">
-        <v>-10.3966767214744</v>
+        <v>-11.73593805611332</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.377092473188271</v>
       </c>
       <c r="E70">
-        <v>-20.52874762824532</v>
+        <v>-22.70808027291068</v>
       </c>
       <c r="F70">
-        <v>-4.474582406540764</v>
+        <v>-4.882849907949723</v>
       </c>
       <c r="G70">
-        <v>-10.97280765112822</v>
+        <v>-12.02096609540795</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.17848363276323</v>
       </c>
       <c r="E71">
-        <v>-18.91563273112902</v>
+        <v>-22.77067284064471</v>
       </c>
       <c r="F71">
-        <v>-4.913186378975046</v>
+        <v>-4.750939854360526</v>
       </c>
       <c r="G71">
-        <v>-11.13975515212813</v>
+        <v>-12.12328512639021</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.970506720476724</v>
       </c>
       <c r="E72">
-        <v>-21.29875576308756</v>
+        <v>-22.53033313963562</v>
       </c>
       <c r="F72">
-        <v>-4.558578861184634</v>
+        <v>-4.814152570868156</v>
       </c>
       <c r="G72">
-        <v>-11.29526140774431</v>
+        <v>-11.65440594057215</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.765794722345085</v>
       </c>
       <c r="E73">
-        <v>-19.9465579528712</v>
+        <v>-22.77828067697759</v>
       </c>
       <c r="F73">
-        <v>-4.675038205976813</v>
+        <v>-4.913501986955512</v>
       </c>
       <c r="G73">
-        <v>-12.07454065386998</v>
+        <v>-11.62323384377437</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.575870864908888</v>
       </c>
       <c r="E74">
-        <v>-19.64877455907482</v>
+        <v>-22.91792070147811</v>
       </c>
       <c r="F74">
-        <v>-4.586481588780532</v>
+        <v>-5.095300467378308</v>
       </c>
       <c r="G74">
-        <v>-11.57910096119035</v>
+        <v>-11.65668028535763</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.412590069590502</v>
       </c>
       <c r="E75">
-        <v>-20.31394852063949</v>
+        <v>-23.20549691486121</v>
       </c>
       <c r="F75">
-        <v>-4.814814436422993</v>
+        <v>-4.951699664633403</v>
       </c>
       <c r="G75">
-        <v>-10.12513253416122</v>
+        <v>-11.77446287455382</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.291682527317078</v>
       </c>
       <c r="E76">
-        <v>-21.92008956778398</v>
+        <v>-22.93051438769345</v>
       </c>
       <c r="F76">
-        <v>-5.156305584757479</v>
+        <v>-4.884951476050625</v>
       </c>
       <c r="G76">
-        <v>-11.55963495341943</v>
+        <v>-11.55378852999708</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.222643465921195</v>
       </c>
       <c r="E77">
-        <v>-22.04248063478929</v>
+        <v>-22.53337174569477</v>
       </c>
       <c r="F77">
-        <v>-5.283482347007078</v>
+        <v>-5.158556258990885</v>
       </c>
       <c r="G77">
-        <v>-11.56853038928345</v>
+        <v>-11.42973245700397</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.209049530724299</v>
       </c>
       <c r="E78">
-        <v>-22.46158184725116</v>
+        <v>-23.2767479248979</v>
       </c>
       <c r="F78">
-        <v>-4.81532553911052</v>
+        <v>-5.202814272587656</v>
       </c>
       <c r="G78">
-        <v>-10.1306445924841</v>
+        <v>-11.3535700463275</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.255897350852102</v>
       </c>
       <c r="E79">
-        <v>-22.84553757293951</v>
+        <v>-24.03195247820907</v>
       </c>
       <c r="F79">
-        <v>-5.056034195750807</v>
+        <v>-5.430211893432357</v>
       </c>
       <c r="G79">
-        <v>-11.08980233048607</v>
+        <v>-11.38066686156643</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.360810127717196</v>
       </c>
       <c r="E80">
-        <v>-21.90257795879632</v>
+        <v>-24.6738998965884</v>
       </c>
       <c r="F80">
-        <v>-5.229112452524332</v>
+        <v>-5.390958047315897</v>
       </c>
       <c r="G80">
-        <v>-10.02647165599986</v>
+        <v>-11.39147248220661</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.513866777500063</v>
       </c>
       <c r="E81">
-        <v>-23.47692458993296</v>
+        <v>-24.6331028742533</v>
       </c>
       <c r="F81">
-        <v>-5.385039362222894</v>
+        <v>-5.61830016754461</v>
       </c>
       <c r="G81">
-        <v>-11.13948699793945</v>
+        <v>-11.38080921502462</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.711152611039465</v>
       </c>
       <c r="E82">
-        <v>-23.88959536930394</v>
+        <v>-25.60744481326965</v>
       </c>
       <c r="F82">
-        <v>-5.506411754081078</v>
+        <v>-5.534657425781735</v>
       </c>
       <c r="G82">
-        <v>-10.88111547132703</v>
+        <v>-10.80189411657227</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.947544351635676</v>
       </c>
       <c r="E83">
-        <v>-24.84621286105427</v>
+        <v>-26.07365121235931</v>
       </c>
       <c r="F83">
-        <v>-5.112174311373335</v>
+        <v>-5.801086890278946</v>
       </c>
       <c r="G83">
-        <v>-11.56238270621703</v>
+        <v>-11.55178564994582</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.216057743163444</v>
       </c>
       <c r="E84">
-        <v>-25.70265597928092</v>
+        <v>-26.32235500486057</v>
       </c>
       <c r="F84">
-        <v>-6.121091016552215</v>
+        <v>-5.84158742933662</v>
       </c>
       <c r="G84">
-        <v>-11.70065095121023</v>
+        <v>-11.06539036767948</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.51756976332928</v>
       </c>
       <c r="E85">
-        <v>-25.46773686165901</v>
+        <v>-27.01584551439521</v>
       </c>
       <c r="F85">
-        <v>-5.524350050188701</v>
+        <v>-5.914900429586584</v>
       </c>
       <c r="G85">
-        <v>-10.92776105797536</v>
+        <v>-10.95833725657607</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.855247172802294</v>
       </c>
       <c r="E86">
-        <v>-26.06045976757497</v>
+        <v>-28.1954314808612</v>
       </c>
       <c r="F86">
-        <v>-5.218613724061251</v>
+        <v>-6.187504544704263</v>
       </c>
       <c r="G86">
-        <v>-9.129376715222612</v>
+        <v>-10.52945608196349</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.229250839788047</v>
       </c>
       <c r="E87">
-        <v>-26.90055962310793</v>
+        <v>-29.29836396779935</v>
       </c>
       <c r="F87">
-        <v>-6.017337170984174</v>
+        <v>-6.283426176478834</v>
       </c>
       <c r="G87">
-        <v>-10.59579610402494</v>
+        <v>-11.00198017842028</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.643525295455015</v>
       </c>
       <c r="E88">
-        <v>-27.38315456963135</v>
+        <v>-29.84663537285601</v>
       </c>
       <c r="F88">
-        <v>-6.20051156966302</v>
+        <v>-6.253152661376124</v>
       </c>
       <c r="G88">
-        <v>-10.97419808025472</v>
+        <v>-10.84106449139293</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.106679442951388</v>
       </c>
       <c r="E89">
-        <v>-29.84792825218521</v>
+        <v>-29.92359905285338</v>
       </c>
       <c r="F89">
-        <v>-5.869215967322192</v>
+        <v>-6.320961988601888</v>
       </c>
       <c r="G89">
-        <v>-10.51935560752317</v>
+        <v>-11.08939844393027</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.620187855841611</v>
       </c>
       <c r="E90">
-        <v>-30.22882046520736</v>
+        <v>-32.07207241139347</v>
       </c>
       <c r="F90">
-        <v>-6.168867106508676</v>
+        <v>-6.770611411985099</v>
       </c>
       <c r="G90">
-        <v>-10.44381888995362</v>
+        <v>-10.15439444618283</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.181400760224555</v>
       </c>
       <c r="E91">
-        <v>-29.74261632489983</v>
+        <v>-33.50905684045545</v>
       </c>
       <c r="F91">
-        <v>-6.466404666266918</v>
+        <v>-7.063904417171396</v>
       </c>
       <c r="G91">
-        <v>-10.39593184872806</v>
+        <v>-11.30700060222657</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.792641855536667</v>
       </c>
       <c r="E92">
-        <v>-31.89456302300381</v>
+        <v>-34.37302175400884</v>
       </c>
       <c r="F92">
-        <v>-6.584606481890887</v>
+        <v>-6.82280518530069</v>
       </c>
       <c r="G92">
-        <v>-11.19123744580934</v>
+        <v>-10.98280549865682</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.446787615560098</v>
       </c>
       <c r="E93">
-        <v>-33.54807417250554</v>
+        <v>-36.57176343827108</v>
       </c>
       <c r="F93">
-        <v>-6.686823705926734</v>
+        <v>-7.066063556806793</v>
       </c>
       <c r="G93">
-        <v>-10.72488751678328</v>
+        <v>-10.95628471834172</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-10.1255659521252</v>
       </c>
       <c r="E94">
-        <v>-35.03782438070488</v>
+        <v>-37.54400642958487</v>
       </c>
       <c r="F94">
-        <v>-6.385468200808989</v>
+        <v>-6.897668889328695</v>
       </c>
       <c r="G94">
-        <v>-11.7008595155792</v>
+        <v>-11.37124504896167</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-10.81648485834591</v>
       </c>
       <c r="E95">
-        <v>-36.18158106082218</v>
+        <v>-39.31186154778027</v>
       </c>
       <c r="F95">
-        <v>-7.028408045594034</v>
+        <v>-7.452124184881503</v>
       </c>
       <c r="G95">
-        <v>-11.64972151863408</v>
+        <v>-11.54848172549763</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-11.49926455258685</v>
       </c>
       <c r="E96">
-        <v>-39.39167816640247</v>
+        <v>-40.62491975714834</v>
       </c>
       <c r="F96">
-        <v>-7.275205616828599</v>
+        <v>-7.322510779916568</v>
       </c>
       <c r="G96">
-        <v>-10.76919254773535</v>
+        <v>-11.55910857667869</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-12.14256993567162</v>
       </c>
       <c r="E97">
-        <v>-40.93269975731666</v>
+        <v>-42.72207418399651</v>
       </c>
       <c r="F97">
-        <v>-6.646719954855002</v>
+        <v>-7.566754494448301</v>
       </c>
       <c r="G97">
-        <v>-9.936057346776822</v>
+        <v>-12.13952997335141</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-12.73041575297245</v>
       </c>
       <c r="E98">
-        <v>-42.72751061704273</v>
+        <v>-44.30737519375771</v>
       </c>
       <c r="F98">
-        <v>-7.527546208538995</v>
+        <v>-7.841174390912916</v>
       </c>
       <c r="G98">
-        <v>-12.51533979242394</v>
+        <v>-12.26979000868511</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-13.23916674604398</v>
       </c>
       <c r="E99">
-        <v>-44.68885837263787</v>
+        <v>-47.0689020422712</v>
       </c>
       <c r="F99">
-        <v>-7.900702529212894</v>
+        <v>-7.822118627178916</v>
       </c>
       <c r="G99">
-        <v>-12.83458231986694</v>
+        <v>-12.37570429212302</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-13.66520552013887</v>
       </c>
       <c r="E100">
-        <v>-45.73542267936554</v>
+        <v>-47.52418123358035</v>
       </c>
       <c r="F100">
-        <v>-8.006878106883018</v>
+        <v>-8.073152883495098</v>
       </c>
       <c r="G100">
-        <v>-12.96281961187614</v>
+        <v>-12.72637051782478</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-13.98289152590759</v>
       </c>
       <c r="E101">
-        <v>-47.77477566397981</v>
+        <v>-50.24987087091564</v>
       </c>
       <c r="F101">
-        <v>-7.741257543154642</v>
+        <v>-8.191650426281866</v>
       </c>
       <c r="G101">
-        <v>-13.17409200710135</v>
+        <v>-12.90765599155527</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-14.22909582833057</v>
       </c>
       <c r="E102">
-        <v>-50.26668735914313</v>
+        <v>-52.36458558784706</v>
       </c>
       <c r="F102">
-        <v>-8.231188402417486</v>
+        <v>-8.163451971523168</v>
       </c>
       <c r="G102">
-        <v>-13.19199874792327</v>
+        <v>-13.46391371633685</v>
       </c>
     </row>
   </sheetData>
